--- a/docs/original/04_Project_Gantt_Chart.xlsx
+++ b/docs/original/04_Project_Gantt_Chart.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>DEV1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="I21" s="7" t="n"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>DEV1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
